--- a/student_marks_analysis.csv.xlsx
+++ b/student_marks_analysis.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEBIN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C12EC5-BB0F-4826-84F9-E57DF15520AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE86F58-57D1-4C7F-884D-19FEB655639A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{65C784B5-9A62-4D1C-BB87-BE82F884FE60}"/>
   </bookViews>
@@ -1011,7 +1011,7 @@
         <v>33</v>
       </c>
       <c r="E2" s="5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F2" s="5">
         <v>30</v>
